--- a/assets/docs/formato.xlsx
+++ b/assets/docs/formato.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nueva carpeta (5)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nick\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78149AFB-0608-DB43-A011-E1B23A67861B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C10A46-33A6-4958-8F90-7E054822D791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="formato" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>MOVIMIENTO</t>
   </si>
@@ -157,19 +156,10 @@
     <t>TESORERA</t>
   </si>
   <si>
-    <t>GONZALEZ GONZALEZ BENJAMIN</t>
-  </si>
-  <si>
-    <t>PRESIDENCIA MUNICIPAL DE COMONFORT                                                                                     ADMINISTRACIÓN 2021-2024</t>
-  </si>
-  <si>
-    <t>C.P MAYRA RAMIREZ ESTRADA</t>
-  </si>
-  <si>
     <t>CLAUDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">CLAUDIO SANTOYO CABELLO </t>
+    <t>PRESIDENCIA MUNICIPAL DE SANTIAGO MARAVATIO                                                                                     ADMINISTRACIÓN 2021-2024</t>
   </si>
 </sst>
 </file>
@@ -177,7 +167,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -514,24 +504,168 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -544,31 +678,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,30 +696,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -612,108 +704,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1054,30 +1044,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V76"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.2265625" customWidth="1"/>
-    <col min="2" max="2" width="0.94140625" customWidth="1"/>
-    <col min="3" max="3" width="10.4921875" customWidth="1"/>
-    <col min="4" max="4" width="9.01171875" customWidth="1"/>
-    <col min="5" max="5" width="1.4765625" customWidth="1"/>
-    <col min="6" max="6" width="4.03515625" customWidth="1"/>
-    <col min="7" max="7" width="2.15234375" customWidth="1"/>
-    <col min="8" max="8" width="10.89453125" customWidth="1"/>
-    <col min="9" max="9" width="3.49609375" customWidth="1"/>
-    <col min="10" max="11" width="1.4765625" customWidth="1"/>
-    <col min="12" max="12" width="7.53125" customWidth="1"/>
-    <col min="13" max="13" width="2.6875" customWidth="1"/>
-    <col min="14" max="14" width="0.94140625" customWidth="1"/>
-    <col min="15" max="15" width="4.9765625" customWidth="1"/>
-    <col min="16" max="16" width="3.09375" customWidth="1"/>
-    <col min="17" max="17" width="10.0859375" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="0.1328125" customWidth="1"/>
-    <col min="20" max="20" width="3.49609375" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" customWidth="1"/>
+    <col min="2" max="2" width="0.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="1.44140625" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="2.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="3.44140625" customWidth="1"/>
+    <col min="10" max="11" width="1.44140625" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" customWidth="1"/>
+    <col min="13" max="13" width="2.6640625" customWidth="1"/>
+    <col min="14" max="14" width="0.88671875" customWidth="1"/>
+    <col min="15" max="15" width="5" customWidth="1"/>
+    <col min="16" max="16" width="3.109375" customWidth="1"/>
+    <col min="17" max="17" width="10.109375" customWidth="1"/>
+    <col min="18" max="18" width="18.77734375" customWidth="1"/>
+    <col min="19" max="19" width="0.109375" customWidth="1"/>
+    <col min="20" max="20" width="3.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="20.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1100,78 +1090,78 @@
       <c r="T1" s="6"/>
       <c r="U1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="70"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="72"/>
       <c r="T2" s="8"/>
       <c r="U2" s="7"/>
     </row>
-    <row r="3" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="73"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="75"/>
       <c r="T3" s="8"/>
       <c r="U3" s="7"/>
     </row>
-    <row r="4" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="76"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="78"/>
       <c r="T4" s="8"/>
       <c r="U4" s="7"/>
     </row>
-    <row r="5" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1194,7 +1184,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="7"/>
     </row>
-    <row r="6" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1217,7 +1207,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="7"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
@@ -1227,22 +1217,22 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="38"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="60"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="8"/>
       <c r="U7" s="7"/>
     </row>
-    <row r="8" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1265,7 +1255,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="7"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
@@ -1275,22 +1265,22 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="38"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="59"/>
+      <c r="N9" s="59"/>
+      <c r="O9" s="59"/>
+      <c r="P9" s="59"/>
+      <c r="Q9" s="60"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="8"/>
       <c r="U9" s="7"/>
     </row>
-    <row r="10" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -1313,7 +1303,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="7"/>
     </row>
-    <row r="11" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -1336,32 +1326,32 @@
       <c r="T11" s="8"/>
       <c r="U11" s="7"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="55"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="97"/>
       <c r="T12" s="8"/>
       <c r="U12" s="7"/>
     </row>
-    <row r="13" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1384,7 +1374,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="7"/>
     </row>
-    <row r="14" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="12"/>
       <c r="C14" s="13"/>
@@ -1407,36 +1397,36 @@
       <c r="T14" s="8"/>
       <c r="U14" s="7"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="15"/>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="56"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="16"/>
       <c r="F15" s="11"/>
       <c r="G15" s="15"/>
-      <c r="H15" s="56" t="s">
+      <c r="H15" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
       <c r="M15" s="16"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="15"/>
-      <c r="Q15" s="56" t="s">
+      <c r="Q15" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="R15" s="56"/>
+      <c r="R15" s="52"/>
       <c r="S15" s="16"/>
       <c r="T15" s="8"/>
       <c r="U15" s="7"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="15"/>
       <c r="C16" s="9" t="s">
@@ -1465,7 +1455,7 @@
       <c r="T16" s="8"/>
       <c r="U16" s="7"/>
     </row>
-    <row r="17" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="15"/>
       <c r="C17" s="9"/>
@@ -1488,7 +1478,7 @@
       <c r="T17" s="8"/>
       <c r="U17" s="7"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="15"/>
       <c r="C18" s="9" t="s">
@@ -1517,7 +1507,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="7"/>
     </row>
-    <row r="19" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="20"/>
       <c r="C19" s="21"/>
@@ -1540,7 +1530,7 @@
       <c r="T19" s="8"/>
       <c r="U19" s="7"/>
     </row>
-    <row r="20" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1563,82 +1553,82 @@
       <c r="T20" s="8"/>
       <c r="U20" s="7"/>
     </row>
-    <row r="21" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="56"/>
       <c r="S21" s="14"/>
       <c r="T21" s="8"/>
       <c r="U21" s="7"/>
     </row>
-    <row r="22" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="60"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
-      <c r="L22" s="77" t="s">
+      <c r="L22" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="60"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="82"/>
       <c r="S22" s="18"/>
       <c r="T22" s="8"/>
       <c r="U22" s="7"/>
     </row>
-    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="15"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="63"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="63"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="85"/>
       <c r="S23" s="18"/>
       <c r="T23" s="8"/>
       <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="15"/>
       <c r="C24" s="9"/>
@@ -1661,34 +1651,34 @@
       <c r="T24" s="8"/>
       <c r="U24" s="7"/>
     </row>
-    <row r="25" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="15"/>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="40"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="100"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="39" t="s">
+      <c r="L25" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="43"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="91"/>
       <c r="S25" s="18"/>
       <c r="T25" s="8"/>
       <c r="U25" s="7"/>
     </row>
-    <row r="26" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="20"/>
       <c r="C26" s="24"/>
@@ -1711,7 +1701,7 @@
       <c r="T26" s="8"/>
       <c r="U26" s="7"/>
     </row>
-    <row r="27" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1734,32 +1724,32 @@
       <c r="T27" s="8"/>
       <c r="U27" s="7"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="55"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="96"/>
+      <c r="S28" s="97"/>
       <c r="T28" s="8"/>
       <c r="U28" s="7"/>
     </row>
-    <row r="29" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="9"/>
       <c r="C29" s="25"/>
@@ -1782,7 +1772,7 @@
       <c r="T29" s="8"/>
       <c r="U29" s="7"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="9"/>
       <c r="C30" s="21"/>
@@ -1790,51 +1780,51 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="11"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
       <c r="L30" s="24"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="57"/>
-      <c r="R30" s="57"/>
-      <c r="S30" s="57"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="51"/>
+      <c r="S30" s="51"/>
       <c r="T30" s="8"/>
       <c r="U30" s="7"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="78" t="s">
+      <c r="H31" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="78" t="s">
+      <c r="N31" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="78"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
       <c r="T31" s="8"/>
       <c r="U31" s="7"/>
     </row>
-    <row r="32" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1857,32 +1847,32 @@
       <c r="T32" s="8"/>
       <c r="U32" s="7"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
-      <c r="M33" s="57"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="57"/>
-      <c r="P33" s="57"/>
-      <c r="Q33" s="57"/>
-      <c r="R33" s="57"/>
-      <c r="S33" s="57"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="51"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
       <c r="T33" s="8" t="s">
         <v>39</v>
       </c>
       <c r="U33" s="7"/>
     </row>
-    <row r="34" spans="1:22" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1905,34 +1895,34 @@
       <c r="T34" s="8"/>
       <c r="U34" s="7"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="9"/>
-      <c r="M35" s="39" t="s">
+      <c r="M35" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="39"/>
-      <c r="S35" s="39"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
       <c r="T35" s="8"/>
       <c r="U35" s="7"/>
     </row>
-    <row r="36" spans="1:22" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1955,11 +1945,11 @@
       <c r="T36" s="8"/>
       <c r="U36" s="7"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="26"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
@@ -1969,45 +1959,45 @@
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
+      <c r="L37" s="51"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="51"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="51"/>
       <c r="S37" s="9"/>
       <c r="T37" s="8"/>
       <c r="U37" s="7"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="39" t="s">
+      <c r="L38" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="39"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
       <c r="S38" s="9"/>
       <c r="T38" s="8"/>
       <c r="U38" s="7"/>
     </row>
-    <row r="39" spans="1:22" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2030,35 +2020,35 @@
       <c r="T39" s="8"/>
       <c r="U39" s="7"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="54"/>
-      <c r="N40" s="54"/>
-      <c r="O40" s="54"/>
-      <c r="P40" s="54"/>
-      <c r="Q40" s="54"/>
-      <c r="R40" s="54"/>
-      <c r="S40" s="55"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="96"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="96"/>
+      <c r="H40" s="96"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="96"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="96"/>
+      <c r="N40" s="96"/>
+      <c r="O40" s="96"/>
+      <c r="P40" s="96"/>
+      <c r="Q40" s="96"/>
+      <c r="R40" s="96"/>
+      <c r="S40" s="97"/>
       <c r="T40" s="8"/>
       <c r="U40" s="7"/>
       <c r="V40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2081,67 +2071,67 @@
       <c r="T41" s="8"/>
       <c r="U41" s="7"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="99" t="s">
+      <c r="C42" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37"/>
-      <c r="M42" s="37"/>
-      <c r="N42" s="37"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="37"/>
-      <c r="S42" s="38"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="59"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="59"/>
+      <c r="O42" s="59"/>
+      <c r="P42" s="59"/>
+      <c r="Q42" s="59"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="60"/>
       <c r="T42" s="8"/>
       <c r="U42" s="7"/>
     </row>
-    <row r="43" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="39"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
       <c r="T43" s="8"/>
       <c r="U43" s="7"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="51"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92"/>
+      <c r="G44" s="92"/>
+      <c r="H44" s="92"/>
+      <c r="I44" s="92"/>
+      <c r="J44" s="93"/>
       <c r="K44" s="9" t="s">
         <v>35</v>
       </c>
@@ -2150,14 +2140,14 @@
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
       <c r="P44" s="9"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="37"/>
-      <c r="S44" s="38"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="59"/>
+      <c r="S44" s="60"/>
       <c r="T44" s="8"/>
       <c r="U44" s="7"/>
       <c r="V44" s="4"/>
     </row>
-    <row r="45" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -2180,32 +2170,32 @@
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
-      <c r="L46" s="56"/>
-      <c r="M46" s="56"/>
-      <c r="N46" s="56"/>
-      <c r="O46" s="56"/>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="56"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="52"/>
+      <c r="O46" s="52"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="52"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
       <c r="T46" s="8"/>
       <c r="U46" s="7"/>
     </row>
-    <row r="47" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="9"/>
       <c r="C47" s="27"/>
@@ -2214,8 +2204,8 @@
       <c r="F47" s="27"/>
       <c r="G47" s="11"/>
       <c r="H47" s="28"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
@@ -2228,59 +2218,59 @@
       <c r="T47" s="8"/>
       <c r="U47" s="7"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="100" t="s">
+      <c r="C48" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="44"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="46"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="63"/>
       <c r="G48" s="11"/>
-      <c r="H48" s="100" t="s">
+      <c r="H48" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="44"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="46"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="62"/>
+      <c r="K48" s="62"/>
+      <c r="L48" s="63"/>
       <c r="M48" s="11"/>
-      <c r="N48" s="84" t="s">
+      <c r="N48" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="O48" s="84"/>
-      <c r="P48" s="84"/>
-      <c r="Q48" s="85"/>
-      <c r="R48" s="44"/>
-      <c r="S48" s="46"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="67"/>
+      <c r="Q48" s="68"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="63"/>
       <c r="T48" s="8"/>
       <c r="U48" s="7"/>
     </row>
-    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="100"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="49"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="66"/>
       <c r="G49" s="11"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="49"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="64"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="66"/>
       <c r="M49" s="23"/>
-      <c r="N49" s="84"/>
-      <c r="O49" s="84"/>
-      <c r="P49" s="84"/>
-      <c r="Q49" s="85"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="49"/>
+      <c r="N49" s="67"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="67"/>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="64"/>
+      <c r="S49" s="66"/>
       <c r="T49" s="8"/>
       <c r="U49" s="7"/>
     </row>
-    <row r="50" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -2303,34 +2293,34 @@
       <c r="T50" s="8"/>
       <c r="U50" s="7"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
-      <c r="L51" s="56" t="s">
+      <c r="L51" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="M51" s="56"/>
-      <c r="N51" s="56"/>
-      <c r="O51" s="56"/>
-      <c r="P51" s="56"/>
-      <c r="Q51" s="56"/>
-      <c r="R51" s="56"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="52"/>
+      <c r="R51" s="52"/>
       <c r="S51" s="11"/>
       <c r="T51" s="8"/>
       <c r="U51" s="7"/>
     </row>
-    <row r="52" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2353,34 +2343,32 @@
       <c r="T52" s="8"/>
       <c r="U52" s="7"/>
     </row>
-    <row r="53" spans="1:21" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="82"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
       <c r="P53" s="9"/>
-      <c r="Q53" s="87" t="s">
-        <v>45</v>
-      </c>
-      <c r="R53" s="88"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="40"/>
       <c r="S53" s="29"/>
       <c r="T53" s="8"/>
       <c r="U53" s="7"/>
     </row>
-    <row r="54" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2392,45 +2380,45 @@
       <c r="I54" s="11"/>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
-      <c r="L54" s="86"/>
-      <c r="M54" s="86"/>
-      <c r="N54" s="86"/>
-      <c r="O54" s="86"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
       <c r="P54" s="9"/>
-      <c r="Q54" s="91"/>
-      <c r="R54" s="92"/>
+      <c r="Q54" s="43"/>
+      <c r="R54" s="44"/>
       <c r="S54" s="29"/>
       <c r="T54" s="8"/>
       <c r="U54" s="7"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
-      <c r="L55" s="86" t="s">
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="M55" s="86"/>
-      <c r="N55" s="86"/>
-      <c r="O55" s="86"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
       <c r="P55" s="9"/>
-      <c r="Q55" s="89"/>
-      <c r="R55" s="90"/>
+      <c r="Q55" s="41"/>
+      <c r="R55" s="42"/>
       <c r="S55" s="29"/>
       <c r="T55" s="8"/>
       <c r="U55" s="7"/>
     </row>
-    <row r="56" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -2442,45 +2430,43 @@
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
-      <c r="L56" s="86"/>
-      <c r="M56" s="86"/>
-      <c r="N56" s="86"/>
-      <c r="O56" s="86"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="38"/>
       <c r="P56" s="9"/>
-      <c r="Q56" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="R56" s="94"/>
+      <c r="Q56" s="45"/>
+      <c r="R56" s="46"/>
       <c r="S56" s="11"/>
       <c r="T56" s="8"/>
       <c r="U56" s="7"/>
     </row>
-    <row r="57" spans="1:21" ht="28.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="86"/>
-      <c r="O57" s="86"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
       <c r="P57" s="9"/>
-      <c r="Q57" s="95"/>
-      <c r="R57" s="96"/>
+      <c r="Q57" s="47"/>
+      <c r="R57" s="48"/>
       <c r="S57" s="33"/>
       <c r="T57" s="8"/>
       <c r="U57" s="7"/>
     </row>
-    <row r="58" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -2497,42 +2483,40 @@
       <c r="N58" s="32"/>
       <c r="O58" s="32"/>
       <c r="P58" s="9"/>
-      <c r="Q58" s="97"/>
-      <c r="R58" s="98"/>
+      <c r="Q58" s="49"/>
+      <c r="R58" s="50"/>
       <c r="S58" s="33"/>
       <c r="T58" s="8"/>
       <c r="U58" s="7"/>
     </row>
-    <row r="59" spans="1:21" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D59" s="34"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="86" t="s">
+      <c r="D59" s="87"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="86"/>
+      <c r="M59" s="38"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="38"/>
       <c r="P59" s="9"/>
-      <c r="Q59" s="87" t="s">
-        <v>43</v>
-      </c>
-      <c r="R59" s="88"/>
+      <c r="Q59" s="39"/>
+      <c r="R59" s="40"/>
       <c r="S59" s="33"/>
       <c r="T59" s="8"/>
       <c r="U59" s="7"/>
     </row>
-    <row r="60" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2544,18 +2528,18 @@
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
-      <c r="L60" s="86"/>
-      <c r="M60" s="86"/>
-      <c r="N60" s="86"/>
-      <c r="O60" s="86"/>
+      <c r="L60" s="38"/>
+      <c r="M60" s="38"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="38"/>
       <c r="P60" s="9"/>
-      <c r="Q60" s="89"/>
-      <c r="R60" s="90"/>
+      <c r="Q60" s="41"/>
+      <c r="R60" s="42"/>
       <c r="S60" s="9"/>
       <c r="T60" s="8"/>
       <c r="U60" s="7"/>
     </row>
-    <row r="61" spans="1:21" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -2578,37 +2562,51 @@
       <c r="T61" s="31"/>
       <c r="U61" s="7"/>
     </row>
-    <row r="62" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="65" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="3:22" x14ac:dyDescent="0.3">
       <c r="V65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="72" spans="3:22" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C72">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D76">
         <v>70</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="D57:K57"/>
-    <mergeCell ref="D43:Q43"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="L38:R38"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="L59:O60"/>
-    <mergeCell ref="Q59:R60"/>
-    <mergeCell ref="L53:O54"/>
-    <mergeCell ref="L55:O57"/>
-    <mergeCell ref="Q53:R55"/>
-    <mergeCell ref="Q56:R58"/>
+    <mergeCell ref="D59:K59"/>
+    <mergeCell ref="H9:Q9"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="D48:F49"/>
+    <mergeCell ref="D44:J44"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="B12:S12"/>
+    <mergeCell ref="B28:S28"/>
+    <mergeCell ref="B40:S40"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="E22:I23"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="B2:S4"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="L22:O23"/>
+    <mergeCell ref="P22:R23"/>
+    <mergeCell ref="H7:Q7"/>
     <mergeCell ref="L37:R37"/>
     <mergeCell ref="L51:R51"/>
     <mergeCell ref="D53:K53"/>
@@ -2625,33 +2623,19 @@
     <mergeCell ref="I47:J47"/>
     <mergeCell ref="M35:S35"/>
     <mergeCell ref="D46:Q46"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="B2:S4"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="L22:O23"/>
-    <mergeCell ref="P22:R23"/>
-    <mergeCell ref="H7:Q7"/>
-    <mergeCell ref="D59:K59"/>
-    <mergeCell ref="H9:Q9"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="D48:F49"/>
-    <mergeCell ref="D44:J44"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="B12:S12"/>
-    <mergeCell ref="B28:S28"/>
-    <mergeCell ref="B40:S40"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="E22:I23"/>
-    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="L59:O60"/>
+    <mergeCell ref="Q59:R60"/>
+    <mergeCell ref="L53:O54"/>
+    <mergeCell ref="L55:O57"/>
+    <mergeCell ref="Q53:R55"/>
+    <mergeCell ref="Q56:R58"/>
+    <mergeCell ref="D57:K57"/>
+    <mergeCell ref="D43:Q43"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="L38:R38"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="H48:H49"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.60750000000000004" top="0.74803149606299213" bottom="0.42749999999999999" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="90" orientation="portrait" r:id="rId1"/>
